--- a/dcf/META.xlsx
+++ b/dcf/META.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1136,25 +1136,25 @@
         <v>11</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>471.5306645380952</v>
+        <v>409.9867712519768</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>451.8138531934233</v>
+        <v>392.9449022695718</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>433.0397390073678</v>
+        <v>376.7166589972691</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>415.1588032642594</v>
+        <v>361.2593352398522</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>398.1243501804601</v>
+        <v>346.5326582863545</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>381.8923337196999</v>
+        <v>332.498639659654</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>366.4211957691781</v>
+        <v>319.1214356549272</v>
       </c>
     </row>
     <row r="6">
@@ -1162,25 +1162,25 @@
         <v>12</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>504.0023301935278</v>
+        <v>437.947261288156</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>482.8219713839529</v>
+        <v>419.6451704020111</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>462.6565438142843</v>
+        <v>402.2189040774721</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>443.452656947599</v>
+        <v>385.6224221967351</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>425.159967003982</v>
+        <v>369.8123108559965</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>407.7309899034129</v>
+        <v>354.7476211698495</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>391.1209264865596</v>
+        <v>340.3897186542662</v>
       </c>
     </row>
     <row r="7">
@@ -1188,25 +1188,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>536.4739958489603</v>
+        <v>465.9077513243352</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>513.8300895744825</v>
+        <v>446.3454385344504</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>492.2733486212007</v>
+        <v>427.721149157675</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>471.7465106309386</v>
+        <v>409.985509153618</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>452.1955838275039</v>
+        <v>393.0919634256384</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>433.5696460871259</v>
+        <v>376.9966026800449</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>415.8206572039412</v>
+        <v>361.6580016536052</v>
       </c>
     </row>
     <row r="8">
@@ -1214,103 +1214,103 @@
         <v>14</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>568.9456615043928</v>
+        <v>493.8682413605143</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>544.838207765012</v>
+        <v>473.0457066668897</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>521.8901534281172</v>
+        <v>453.223394237878</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>500.0403643142782</v>
+        <v>434.3485961105008</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>479.2312006510257</v>
+        <v>416.3716159952802</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>459.4083022708388</v>
+        <v>399.2455841902403</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>440.5203879213227</v>
+        <v>382.9262846529441</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
         <v>15</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>601.4173271598254</v>
+      <c r="B9" s="53" t="n">
+        <v>521.8287313966935</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>575.8463259555416</v>
+        <v>499.7459747993289</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>551.5069582350336</v>
+        <v>478.7256393180809</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>528.3342179976178</v>
+        <v>458.7116830673835</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>506.2668174745477</v>
+        <v>439.6512685649221</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>485.2469584545518</v>
+        <v>421.4945657004357</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>465.2201186387042</v>
+        <v>404.1945676522831</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
         <v>16</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>633.8889928152579</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>606.8544441460713</v>
+      <c r="B10" s="53" t="n">
+        <v>549.7892214328726</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>526.4462429317683</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>581.12376304195</v>
+        <v>504.2278843982838</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>556.6280716809574</v>
+        <v>483.0747700242664</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>533.3024342980697</v>
+        <v>462.930921134564</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>511.0856146382649</v>
+        <v>443.7435472106311</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>489.9198493560858</v>
+        <v>425.462850651622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
         <v>17</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>666.3606584706904</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>637.8625623366009</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>610.7405678488664</v>
+      <c r="B11" s="53" t="n">
+        <v>577.7497114690518</v>
+      </c>
+      <c r="C11" s="53" t="n">
+        <v>553.1465110642076</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>529.7301294784869</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>584.9219253642971</v>
+        <v>507.4378569811493</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>560.3380511215914</v>
+        <v>486.210573704206</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>536.9242708219778</v>
+        <v>465.9925287208266</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>514.6195800734673</v>
+        <v>446.7311336509611</v>
       </c>
     </row>
     <row r="13">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.7628847987077934</v>
+        <v>0.758522019087344</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24441,7 +24441,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24593,13 +24593,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>500.0403643142782</v>
+        <v>434.3485961105008</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>708.0415151484198</v>
+        <v>600.8664420484578</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>343.5785597302267</v>
+        <v>305.5718475611439</v>
       </c>
     </row>
     <row r="59">
